--- a/Excel/MaskData.xlsx
+++ b/Excel/MaskData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="113">
   <si>
     <t>int</t>
   </si>
@@ -104,6 +104,12 @@
     <t>面具接近和逃离的速度</t>
   </si>
   <si>
+    <t>不戴面具的资源对应的资源表的id</t>
+  </si>
+  <si>
+    <t>戴面具的资源对应的资源表的id</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -153,6 +159,12 @@
   </si>
   <si>
     <t>moveSpeed</t>
+  </si>
+  <si>
+    <t>resIdNoMask</t>
+  </si>
+  <si>
+    <t>resIdWithMask</t>
   </si>
   <si>
     <t>E_World</t>
@@ -1513,7 +1525,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1531,10 +1543,12 @@
     <col min="15" max="15" width="14.5555555555556" style="1" customWidth="1"/>
     <col min="16" max="16" width="12" style="1" customWidth="1"/>
     <col min="17" max="17" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.23148148148148" style="1"/>
+    <col min="18" max="18" width="13.1111111111111" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.23148148148148" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:17">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1586,8 +1600,14 @@
       <c r="Q1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="101" customHeight="1" spans="1:17">
+    <row r="2" s="1" customFormat="1" ht="85" customHeight="1" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1639,63 +1659,75 @@
       <c r="Q2" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="R2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:17">
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:17">
+    <row r="4" s="1" customFormat="1" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -1706,35 +1738,35 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:17">
+    <row r="5" s="1" customFormat="1" spans="1:19">
       <c r="A5" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:17">
+    <row r="6" s="1" customFormat="1" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:17">
+    <row r="7" s="1" customFormat="1" spans="1:19">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1">
         <v>0</v>
@@ -1779,103 +1811,103 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:17">
+    <row r="8" s="1" customFormat="1" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:17">
+    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:17">
+    <row r="10" s="1" customFormat="1" spans="1:19">
       <c r="A10" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
@@ -1895,53 +1927,53 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:17">
+    <row r="11" s="1" customFormat="1" spans="1:19">
       <c r="A11" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:17">
+    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:17">
+    <row r="13" s="1" customFormat="1" spans="1:19">
       <c r="A13" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B13" s="1">
         <v>0</v>
@@ -1952,38 +1984,38 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:17">
+    <row r="14" s="1" customFormat="1" spans="1:19">
       <c r="A14" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:17">
+    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:17">
+    <row r="19" s="1" customFormat="1" spans="1:19">
       <c r="A19" s="1">
         <v>10001</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C19" s="3">
         <v>1</v>
@@ -1992,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F19" s="1">
         <v>5</v>
@@ -2004,7 +2036,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J19" s="1" t="b">
         <v>1</v>
@@ -2030,13 +2062,19 @@
       <c r="Q19" s="1">
         <v>3</v>
       </c>
+      <c r="R19" s="1">
+        <v>10014</v>
+      </c>
+      <c r="S19" s="1">
+        <v>10015</v>
+      </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="1:17">
+    <row r="20" s="1" customFormat="1" spans="1:19">
       <c r="A20" s="1">
         <v>20001</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C20" s="3">
         <v>0</v>
@@ -2045,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -2057,7 +2095,7 @@
         <v>1</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J20" s="1" t="b">
         <v>1</v>
@@ -2083,13 +2121,19 @@
       <c r="Q20" s="1">
         <v>3</v>
       </c>
+      <c r="R20" s="1">
+        <v>10003</v>
+      </c>
+      <c r="S20" s="1">
+        <v>10004</v>
+      </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="1:17">
+    <row r="21" s="1" customFormat="1" spans="1:19">
       <c r="A21" s="1">
         <v>10002</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C21" s="3">
         <v>0</v>
@@ -2098,7 +2142,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F21" s="1">
         <v>7</v>
@@ -2110,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J21" s="1" t="b">
         <v>1</v>
@@ -2136,13 +2180,19 @@
       <c r="Q21" s="1">
         <v>3</v>
       </c>
+      <c r="R21" s="1">
+        <v>10020</v>
+      </c>
+      <c r="S21" s="1">
+        <v>10021</v>
+      </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:17">
+    <row r="22" s="1" customFormat="1" spans="1:19">
       <c r="A22" s="1">
         <v>10003</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C22" s="3">
         <v>0</v>
@@ -2151,7 +2201,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F22" s="1">
         <v>7</v>
@@ -2163,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J22" s="1" t="b">
         <v>1</v>
@@ -2189,13 +2239,19 @@
       <c r="Q22" s="1">
         <v>3</v>
       </c>
+      <c r="R22" s="1">
+        <v>10009</v>
+      </c>
+      <c r="S22" s="1">
+        <v>10010</v>
+      </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:17">
+    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A23" s="1">
         <v>10004</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C23" s="3">
         <v>0</v>
@@ -2204,7 +2260,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F23" s="1">
         <v>5</v>
@@ -2216,7 +2272,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J23" s="1" t="b">
         <v>1</v>
@@ -2242,13 +2298,19 @@
       <c r="Q23" s="1">
         <v>3</v>
       </c>
+      <c r="R23" s="1">
+        <v>10007</v>
+      </c>
+      <c r="S23" s="1">
+        <v>10008</v>
+      </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="1:17">
+    <row r="24" s="1" customFormat="1" spans="1:19">
       <c r="A24" s="1">
         <v>10005</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C24" s="3">
         <v>0</v>
@@ -2257,7 +2319,7 @@
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F24" s="1">
         <v>5</v>
@@ -2269,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J24" s="1" t="b">
         <v>1</v>
@@ -2295,13 +2357,19 @@
       <c r="Q24" s="1">
         <v>3</v>
       </c>
+      <c r="R24" s="1">
+        <v>10011</v>
+      </c>
+      <c r="S24" s="1">
+        <v>10012</v>
+      </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="28.8" spans="1:17">
+    <row r="25" s="2" customFormat="1" ht="28.8" spans="1:19">
       <c r="A25" s="2">
         <v>20002</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -2310,7 +2378,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -2322,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J25" s="2" t="b">
         <v>1</v>
@@ -2348,13 +2416,19 @@
       <c r="Q25" s="1">
         <v>3</v>
       </c>
+      <c r="R25" s="2">
+        <v>10005</v>
+      </c>
+      <c r="S25" s="2">
+        <v>10006</v>
+      </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="1:17">
+    <row r="26" s="1" customFormat="1" spans="1:19">
       <c r="A26" s="1">
         <v>20003</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C26" s="3">
         <v>0</v>
@@ -2363,7 +2437,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2375,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J26" s="1" t="b">
         <v>1</v>
@@ -2401,13 +2475,19 @@
       <c r="Q26" s="1">
         <v>3</v>
       </c>
+      <c r="R26" s="1">
+        <v>10016</v>
+      </c>
+      <c r="S26" s="1">
+        <v>10017</v>
+      </c>
     </row>
-    <row r="27" s="2" customFormat="1" ht="28.8" spans="1:17">
+    <row r="27" s="2" customFormat="1" ht="28.8" spans="1:19">
       <c r="A27" s="2">
         <v>20004</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -2416,7 +2496,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2428,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2454,13 +2534,19 @@
       <c r="Q27" s="1">
         <v>3</v>
       </c>
+      <c r="R27" s="2">
+        <v>10018</v>
+      </c>
+      <c r="S27" s="2">
+        <v>10019</v>
+      </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:17">
+    <row r="28" s="1" customFormat="1" spans="1:19">
       <c r="A28" s="1">
         <v>20005</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C28" s="3">
         <v>0</v>
@@ -2469,7 +2555,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2481,7 +2567,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J28" s="1" t="b">
         <v>1</v>
@@ -2507,13 +2593,19 @@
       <c r="Q28" s="1">
         <v>3</v>
       </c>
+      <c r="R28" s="1">
+        <v>10001</v>
+      </c>
+      <c r="S28" s="1">
+        <v>10002</v>
+      </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:17">
+    <row r="29" s="1" customFormat="1" spans="1:19">
       <c r="A29" s="1">
         <v>20006</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C29" s="3">
         <v>0</v>
@@ -2522,7 +2614,7 @@
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2534,7 +2626,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J29" s="1" t="b">
         <v>1</v>
@@ -2560,13 +2652,19 @@
       <c r="Q29" s="1">
         <v>3</v>
       </c>
+      <c r="R29" s="1">
+        <v>10024</v>
+      </c>
+      <c r="S29" s="1">
+        <v>10024</v>
+      </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="1:17">
+    <row r="30" s="1" customFormat="1" spans="1:19">
       <c r="A30" s="1">
         <v>20007</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C30" s="3">
         <v>0</v>
@@ -2575,7 +2673,7 @@
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2587,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J30" s="1" t="b">
         <v>1</v>
@@ -2613,13 +2711,19 @@
       <c r="Q30" s="1">
         <v>3</v>
       </c>
+      <c r="R30" s="1">
+        <v>10023</v>
+      </c>
+      <c r="S30" s="1">
+        <v>10023</v>
+      </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="1:17">
+    <row r="31" s="1" customFormat="1" spans="1:19">
       <c r="A31" s="1">
         <v>10006</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C31" s="3">
         <v>0</v>
@@ -2628,7 +2732,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2640,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J31" s="1" t="b">
         <v>1</v>
@@ -2666,13 +2770,19 @@
       <c r="Q31" s="1">
         <v>3</v>
       </c>
+      <c r="R31" s="1">
+        <v>10022</v>
+      </c>
+      <c r="S31" s="1">
+        <v>10022</v>
+      </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="1:17">
+    <row r="32" s="1" customFormat="1" spans="1:19">
       <c r="A32" s="1">
         <v>10007</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C32" s="3">
         <v>0</v>
@@ -2681,7 +2791,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2693,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="J32" s="1" t="b">
         <v>1</v>
@@ -2718,6 +2828,12 @@
       </c>
       <c r="Q32" s="1">
         <v>3</v>
+      </c>
+      <c r="R32" s="1">
+        <v>10013</v>
+      </c>
+      <c r="S32" s="1">
+        <v>10013</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MaskData.xlsx
+++ b/Excel/MaskData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowHeight="15000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
   <si>
     <t>int</t>
   </si>
@@ -35,18 +35,9 @@
     <t>string</t>
   </si>
   <si>
-    <t>enum:E_World</t>
-  </si>
-  <si>
     <t>enum:E_MaskType</t>
   </si>
   <si>
-    <t>enum:E_InputAction</t>
-  </si>
-  <si>
-    <t>enum:E_SpAbility</t>
-  </si>
-  <si>
     <t>bool</t>
   </si>
   <si>
@@ -59,7 +50,7 @@
     <t>这个面具对应的描述</t>
   </si>
   <si>
-    <t>面具对应的世界类型</t>
+    <t>面具对应资源表的预制体资源id</t>
   </si>
   <si>
     <t>可以附身的面具类型</t>
@@ -71,10 +62,10 @@
     <t>初始的理智值</t>
   </si>
   <si>
-    <t>面具对应的输入方式</t>
-  </si>
-  <si>
-    <t>面具对应的特殊能力</t>
+    <t>面具是否可以移动</t>
+  </si>
+  <si>
+    <t>面具在里世界会显示在头顶的图标</t>
   </si>
   <si>
     <t>体积</t>
@@ -116,7 +107,7 @@
     <t>des</t>
   </si>
   <si>
-    <t>worldType</t>
+    <t>resPrefab</t>
   </si>
   <si>
     <t>maskType</t>
@@ -128,10 +119,10 @@
     <t>startLizi</t>
   </si>
   <si>
-    <t>inputAction</t>
-  </si>
-  <si>
-    <t>spType</t>
+    <t>canMove</t>
+  </si>
+  <si>
+    <t>resSoul</t>
   </si>
   <si>
     <t>volume</t>
@@ -167,24 +158,6 @@
     <t>resIdWithMask</t>
   </si>
   <si>
-    <t>E_World</t>
-  </si>
-  <si>
-    <t>In_World</t>
-  </si>
-  <si>
-    <t>Out_World</t>
-  </si>
-  <si>
-    <t>世界类型</t>
-  </si>
-  <si>
-    <t>里世界</t>
-  </si>
-  <si>
-    <t>表世界</t>
-  </si>
-  <si>
     <t>E_MaskType</t>
   </si>
   <si>
@@ -270,51 +243,6 @@
   </si>
   <si>
     <t>面具</t>
-  </si>
-  <si>
-    <t>E_InputAction</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>WASD</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>不能移动</t>
-  </si>
-  <si>
-    <t>WASD移动</t>
-  </si>
-  <si>
-    <t>鼠标</t>
-  </si>
-  <si>
-    <t>X轴水平移动</t>
-  </si>
-  <si>
-    <t>Y轴竖直移动</t>
-  </si>
-  <si>
-    <t>E_SpAbility</t>
-  </si>
-  <si>
-    <t>Normal</t>
-  </si>
-  <si>
-    <t>Save</t>
-  </si>
-  <si>
-    <t>无特殊能力</t>
-  </si>
-  <si>
-    <t>磁带的保存</t>
   </si>
   <si>
     <t>Sprites/Mouse</t>
@@ -378,10 +306,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -857,137 +791,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -998,6 +932,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1526,29 +1469,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S32"/>
-  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3055555555556" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.3055555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.9907407407407" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.212962962963" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6666666666667" style="3" customWidth="1"/>
-    <col min="8" max="8" width="24.4444444444444" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13.6111111111111" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.8518518518519" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.1111111111111" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.2222222222222" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5555555555556" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3076923076923" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.3076923076923" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.9903846153846" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.2115384615385" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6634615384615" style="4" customWidth="1"/>
+    <col min="8" max="8" width="24.4423076923077" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.7788461538462" style="1" customWidth="1"/>
+    <col min="10" max="11" width="13.6153846153846" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.8557692307692" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.1153846153846" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.2211538461538" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5576923076923" style="1" customWidth="1"/>
     <col min="16" max="16" width="12" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.1111111111111" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.23148148148148" style="1"/>
+    <col min="17" max="17" width="13.5576923076923" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.1153846153846" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.3365384615385" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.23076923076923" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="34" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1556,49 +1499,49 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>0</v>
@@ -1609,434 +1552,352 @@
     </row>
     <row r="2" s="1" customFormat="1" ht="85" customHeight="1" spans="1:19">
       <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="G2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="1" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="17" spans="1:19">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:19">
-      <c r="A3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q3" s="1" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" ht="17" spans="1:19">
+      <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="B4" s="1">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6">
+        <v>5</v>
+      </c>
+      <c r="H4" s="1">
+        <v>6</v>
+      </c>
+      <c r="I4" s="1">
+        <v>7</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1">
+        <v>9</v>
+      </c>
+      <c r="L4" s="1">
+        <v>10</v>
+      </c>
+      <c r="M4" s="1">
+        <v>11</v>
+      </c>
+      <c r="N4" s="1">
+        <v>12</v>
+      </c>
+      <c r="O4" s="1">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="17" spans="1:19">
+      <c r="A5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:19">
-      <c r="A4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="1">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:19">
-      <c r="A5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:19">
+      <c r="G5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="34" spans="1:19">
       <c r="A6" s="1" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:19">
-      <c r="A7" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>1</v>
-      </c>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1">
-        <v>4</v>
-      </c>
-      <c r="G7" s="1">
-        <v>5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>6</v>
-      </c>
-      <c r="I7" s="1">
-        <v>7</v>
-      </c>
-      <c r="J7" s="1">
-        <v>8</v>
-      </c>
-      <c r="K7" s="1">
-        <v>9</v>
-      </c>
-      <c r="L7" s="1">
-        <v>10</v>
-      </c>
-      <c r="M7" s="1">
-        <v>11</v>
-      </c>
-      <c r="N7" s="1">
-        <v>12</v>
-      </c>
-      <c r="O7" s="1">
-        <v>13</v>
-      </c>
+      <c r="C7" s="3"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:19">
-      <c r="A8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="28.8" spans="1:19">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:19">
+      <c r="C9" s="3"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:19">
-      <c r="A10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="4"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:19">
-      <c r="A11" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="4"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" s="1" customFormat="1" ht="28.8" spans="1:19">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="3"/>
+    <row r="12" s="1" customFormat="1" spans="1:19">
+      <c r="C12" s="3"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="4"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:19">
-      <c r="A13" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="1">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>1</v>
-      </c>
-      <c r="G13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="G13" s="4"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:19">
-      <c r="A14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="G14" s="4"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" s="1" customFormat="1" ht="28.8" spans="1:19">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="3"/>
+    <row r="15" s="1" customFormat="1" spans="1:19">
+      <c r="C15" s="3"/>
+      <c r="G15" s="4"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:19">
+    <row r="19" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A19" s="1">
         <v>10001</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C19" s="3">
-        <v>1</v>
+        <v>20001</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="F19" s="1">
         <v>5</v>
       </c>
-      <c r="G19" s="3">
-        <v>0</v>
+      <c r="G19" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="H19" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J19" s="1" t="b">
         <v>1</v>
@@ -2069,33 +1930,33 @@
         <v>10015</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" spans="1:19">
+    <row r="20" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A20" s="1">
         <v>20001</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>1</v>
+        <v>10026</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="J20" s="1" t="b">
         <v>1</v>
@@ -2128,33 +1989,33 @@
         <v>10004</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" spans="1:19">
+    <row r="21" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A21" s="1">
         <v>10002</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="C21" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F21" s="1">
         <v>7</v>
       </c>
-      <c r="G21" s="3">
-        <v>0</v>
+      <c r="G21" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="H21" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J21" s="1" t="b">
         <v>1</v>
@@ -2187,33 +2048,33 @@
         <v>10021</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" spans="1:19">
+    <row r="22" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A22" s="1">
         <v>10003</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C22" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="F22" s="1">
         <v>7</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
+      <c r="G22" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J22" s="1" t="b">
         <v>1</v>
@@ -2246,33 +2107,33 @@
         <v>10010</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:19">
+    <row r="23" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A23" s="1">
         <v>10004</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D23" s="1">
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="F23" s="1">
         <v>5</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
+      <c r="G23" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="H23" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="J23" s="1" t="b">
         <v>1</v>
@@ -2305,33 +2166,33 @@
         <v>10008</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" spans="1:19">
+    <row r="24" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A24" s="1">
         <v>10005</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C24" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D24" s="1">
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="F24" s="1">
         <v>5</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="G24" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="H24" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="J24" s="1" t="b">
         <v>1</v>
@@ -2364,33 +2225,33 @@
         <v>10012</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="28.8" spans="1:19">
+    <row r="25" s="2" customFormat="1" ht="17" spans="1:19">
       <c r="A25" s="2">
         <v>20002</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0</v>
+        <v>64</v>
+      </c>
+      <c r="C25" s="3">
+        <v>20001</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0</v>
+      <c r="G25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>10026</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J25" s="2" t="b">
         <v>1</v>
@@ -2423,33 +2284,33 @@
         <v>10006</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" spans="1:19">
+    <row r="26" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A26" s="1">
         <v>20003</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C26" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D26" s="1">
         <v>7</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J26" s="1" t="b">
         <v>1</v>
@@ -2482,33 +2343,33 @@
         <v>10017</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" ht="28.8" spans="1:19">
+    <row r="27" s="2" customFormat="1" ht="17" spans="1:19">
       <c r="A27" s="2">
         <v>20004</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="2">
-        <v>0</v>
+        <v>66</v>
+      </c>
+      <c r="C27" s="3">
+        <v>20001</v>
       </c>
       <c r="D27" s="2">
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
       </c>
-      <c r="G27" s="2">
-        <v>0</v>
-      </c>
-      <c r="H27" s="2">
-        <v>0</v>
+      <c r="G27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>10026</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2541,33 +2402,33 @@
         <v>10019</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:19">
+    <row r="28" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A28" s="1">
         <v>20005</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C28" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D28" s="1">
         <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J28" s="1" t="b">
         <v>1</v>
@@ -2600,33 +2461,33 @@
         <v>10002</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:19">
+    <row r="29" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A29" s="1">
         <v>20006</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C29" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D29" s="1">
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J29" s="1" t="b">
         <v>1</v>
@@ -2659,33 +2520,33 @@
         <v>10024</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="1:19">
+    <row r="30" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A30" s="1">
         <v>20007</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C30" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D30" s="1">
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
       </c>
-      <c r="G30" s="3">
-        <v>0</v>
+      <c r="G30" s="6" t="b">
+        <v>1</v>
       </c>
       <c r="H30" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="J30" s="1" t="b">
         <v>1</v>
@@ -2718,33 +2579,33 @@
         <v>10023</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="1:19">
+    <row r="31" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A31" s="1">
         <v>10006</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C31" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D31" s="1">
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="3">
-        <v>0</v>
+        <v>10026</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J31" s="1" t="b">
         <v>1</v>
@@ -2777,33 +2638,33 @@
         <v>10022</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" spans="1:19">
+    <row r="32" s="1" customFormat="1" ht="17" spans="1:19">
       <c r="A32" s="1">
         <v>10007</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C32" s="3">
-        <v>0</v>
+        <v>20001</v>
       </c>
       <c r="D32" s="1">
         <v>13</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="6" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>10025</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="J32" s="1" t="b">
         <v>1</v>

--- a/Excel/MaskData.xlsx
+++ b/Excel/MaskData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15000"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -921,7 +921,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -932,9 +932,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1469,29 +1466,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:S32"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3076923076923" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.3076923076923" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.9903846153846" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.2115384615385" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19.6634615384615" style="4" customWidth="1"/>
-    <col min="8" max="8" width="24.4423076923077" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.7788461538462" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13.6153846153846" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.8557692307692" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.1153846153846" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.2211538461538" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5576923076923" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3055555555556" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.3055555555556" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.9907407407407" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.212962962963" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19.6666666666667" style="4" customWidth="1"/>
+    <col min="8" max="8" width="24.4444444444444" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.7777777777778" style="1" customWidth="1"/>
+    <col min="10" max="11" width="13.6111111111111" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.8518518518519" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.1111111111111" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.2222222222222" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5555555555556" style="1" customWidth="1"/>
     <col min="16" max="16" width="12" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5576923076923" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.1153846153846" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.3365384615385" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.23076923076923" style="1"/>
+    <col min="17" max="17" width="13.5555555555556" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.1111111111111" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.3333333333333" style="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.23148148148148" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="34" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1510,11 +1507,11 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
@@ -1569,7 +1566,7 @@
       <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -1609,7 +1606,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="3" s="1" customFormat="1" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,7 +1625,7 @@
       <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H3" s="3" t="s">
@@ -1668,7 +1665,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="4" s="1" customFormat="1" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>43</v>
       </c>
@@ -1687,7 +1684,7 @@
       <c r="F4" s="1">
         <v>4</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>5</v>
       </c>
       <c r="H4" s="1">
@@ -1715,7 +1712,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="5" s="1" customFormat="1" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
@@ -1734,7 +1731,7 @@
       <c r="F5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>49</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -1762,7 +1759,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="34" spans="1:19">
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -1781,7 +1778,7 @@
       <c r="F6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>63</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -1814,14 +1811,14 @@
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="6"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" s="1" customFormat="1" spans="1:19">
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="5"/>
+      <c r="G8" s="4"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" s="1" customFormat="1" spans="1:19">
@@ -1829,7 +1826,7 @@
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="4"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:19">
@@ -1871,7 +1868,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="19" s="1" customFormat="1" spans="1:19">
       <c r="A19" s="1">
         <v>10001</v>
       </c>
@@ -1890,7 +1887,7 @@
       <c r="F19" s="1">
         <v>5</v>
       </c>
-      <c r="G19" s="6" t="b">
+      <c r="G19" s="5" t="b">
         <v>1</v>
       </c>
       <c r="H19" s="3">
@@ -1930,7 +1927,7 @@
         <v>10015</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="20" s="1" customFormat="1" spans="1:19">
       <c r="A20" s="1">
         <v>20001</v>
       </c>
@@ -1938,7 +1935,7 @@
         <v>59</v>
       </c>
       <c r="C20" s="3">
-        <v>20001</v>
+        <v>20002</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -1949,7 +1946,7 @@
       <c r="F20" s="1">
         <v>0</v>
       </c>
-      <c r="G20" s="6" t="b">
+      <c r="G20" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H20" s="3">
@@ -1989,7 +1986,7 @@
         <v>10004</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="21" s="1" customFormat="1" spans="1:19">
       <c r="A21" s="1">
         <v>10002</v>
       </c>
@@ -1997,7 +1994,7 @@
         <v>60</v>
       </c>
       <c r="C21" s="3">
-        <v>20001</v>
+        <v>20003</v>
       </c>
       <c r="D21" s="1">
         <v>2</v>
@@ -2008,7 +2005,7 @@
       <c r="F21" s="1">
         <v>7</v>
       </c>
-      <c r="G21" s="6" t="b">
+      <c r="G21" s="5" t="b">
         <v>1</v>
       </c>
       <c r="H21" s="3">
@@ -2048,7 +2045,7 @@
         <v>10021</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="22" s="1" customFormat="1" spans="1:19">
       <c r="A22" s="1">
         <v>10003</v>
       </c>
@@ -2056,7 +2053,7 @@
         <v>61</v>
       </c>
       <c r="C22" s="3">
-        <v>20001</v>
+        <v>20004</v>
       </c>
       <c r="D22" s="1">
         <v>3</v>
@@ -2067,7 +2064,7 @@
       <c r="F22" s="1">
         <v>7</v>
       </c>
-      <c r="G22" s="6" t="b">
+      <c r="G22" s="5" t="b">
         <v>1</v>
       </c>
       <c r="H22" s="3">
@@ -2107,7 +2104,7 @@
         <v>10010</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:19">
       <c r="A23" s="1">
         <v>10004</v>
       </c>
@@ -2115,7 +2112,7 @@
         <v>62</v>
       </c>
       <c r="C23" s="3">
-        <v>20001</v>
+        <v>20005</v>
       </c>
       <c r="D23" s="1">
         <v>4</v>
@@ -2126,7 +2123,7 @@
       <c r="F23" s="1">
         <v>5</v>
       </c>
-      <c r="G23" s="6" t="b">
+      <c r="G23" s="5" t="b">
         <v>1</v>
       </c>
       <c r="H23" s="3">
@@ -2166,7 +2163,7 @@
         <v>10008</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="24" s="1" customFormat="1" spans="1:19">
       <c r="A24" s="1">
         <v>10005</v>
       </c>
@@ -2174,7 +2171,7 @@
         <v>63</v>
       </c>
       <c r="C24" s="3">
-        <v>20001</v>
+        <v>20006</v>
       </c>
       <c r="D24" s="1">
         <v>5</v>
@@ -2185,7 +2182,7 @@
       <c r="F24" s="1">
         <v>5</v>
       </c>
-      <c r="G24" s="6" t="b">
+      <c r="G24" s="5" t="b">
         <v>1</v>
       </c>
       <c r="H24" s="3">
@@ -2225,7 +2222,7 @@
         <v>10012</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="17" spans="1:19">
+    <row r="25" s="2" customFormat="1" ht="28.8" spans="1:19">
       <c r="A25" s="2">
         <v>20002</v>
       </c>
@@ -2233,7 +2230,7 @@
         <v>64</v>
       </c>
       <c r="C25" s="3">
-        <v>20001</v>
+        <v>20007</v>
       </c>
       <c r="D25" s="2">
         <v>6</v>
@@ -2244,7 +2241,7 @@
       <c r="F25" s="2">
         <v>0</v>
       </c>
-      <c r="G25" s="6" t="b">
+      <c r="G25" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H25" s="3">
@@ -2284,7 +2281,7 @@
         <v>10006</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="26" s="1" customFormat="1" spans="1:19">
       <c r="A26" s="1">
         <v>20003</v>
       </c>
@@ -2292,7 +2289,7 @@
         <v>65</v>
       </c>
       <c r="C26" s="3">
-        <v>20001</v>
+        <v>20008</v>
       </c>
       <c r="D26" s="1">
         <v>7</v>
@@ -2303,7 +2300,7 @@
       <c r="F26" s="1">
         <v>0</v>
       </c>
-      <c r="G26" s="6" t="b">
+      <c r="G26" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="3">
@@ -2343,7 +2340,7 @@
         <v>10017</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" ht="17" spans="1:19">
+    <row r="27" s="2" customFormat="1" ht="28.8" spans="1:19">
       <c r="A27" s="2">
         <v>20004</v>
       </c>
@@ -2351,7 +2348,7 @@
         <v>66</v>
       </c>
       <c r="C27" s="3">
-        <v>20001</v>
+        <v>20009</v>
       </c>
       <c r="D27" s="2">
         <v>8</v>
@@ -2362,7 +2359,7 @@
       <c r="F27" s="1">
         <v>0</v>
       </c>
-      <c r="G27" s="6" t="b">
+      <c r="G27" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H27" s="3">
@@ -2402,7 +2399,7 @@
         <v>10019</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="28" s="1" customFormat="1" spans="1:19">
       <c r="A28" s="1">
         <v>20005</v>
       </c>
@@ -2410,7 +2407,7 @@
         <v>67</v>
       </c>
       <c r="C28" s="3">
-        <v>20001</v>
+        <v>20010</v>
       </c>
       <c r="D28" s="1">
         <v>9</v>
@@ -2421,7 +2418,7 @@
       <c r="F28" s="1">
         <v>0</v>
       </c>
-      <c r="G28" s="6" t="b">
+      <c r="G28" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="3">
@@ -2461,7 +2458,7 @@
         <v>10002</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="29" s="1" customFormat="1" spans="1:19">
       <c r="A29" s="1">
         <v>20006</v>
       </c>
@@ -2469,7 +2466,7 @@
         <v>68</v>
       </c>
       <c r="C29" s="3">
-        <v>20001</v>
+        <v>20011</v>
       </c>
       <c r="D29" s="1">
         <v>10</v>
@@ -2480,7 +2477,7 @@
       <c r="F29" s="1">
         <v>0</v>
       </c>
-      <c r="G29" s="6" t="b">
+      <c r="G29" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H29" s="3">
@@ -2520,7 +2517,7 @@
         <v>10024</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="30" s="1" customFormat="1" spans="1:19">
       <c r="A30" s="1">
         <v>20007</v>
       </c>
@@ -2528,7 +2525,7 @@
         <v>69</v>
       </c>
       <c r="C30" s="3">
-        <v>20001</v>
+        <v>20012</v>
       </c>
       <c r="D30" s="1">
         <v>11</v>
@@ -2539,7 +2536,7 @@
       <c r="F30" s="1">
         <v>0</v>
       </c>
-      <c r="G30" s="6" t="b">
+      <c r="G30" s="5" t="b">
         <v>1</v>
       </c>
       <c r="H30" s="3">
@@ -2579,7 +2576,7 @@
         <v>10023</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="31" s="1" customFormat="1" spans="1:19">
       <c r="A31" s="1">
         <v>10006</v>
       </c>
@@ -2587,7 +2584,7 @@
         <v>70</v>
       </c>
       <c r="C31" s="3">
-        <v>20001</v>
+        <v>20011</v>
       </c>
       <c r="D31" s="1">
         <v>12</v>
@@ -2598,7 +2595,7 @@
       <c r="F31" s="1">
         <v>0</v>
       </c>
-      <c r="G31" s="6" t="b">
+      <c r="G31" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H31" s="3">
@@ -2638,7 +2635,7 @@
         <v>10022</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="17" spans="1:19">
+    <row r="32" s="1" customFormat="1" spans="1:19">
       <c r="A32" s="1">
         <v>10007</v>
       </c>
@@ -2646,7 +2643,7 @@
         <v>71</v>
       </c>
       <c r="C32" s="3">
-        <v>20001</v>
+        <v>20011</v>
       </c>
       <c r="D32" s="1">
         <v>13</v>
@@ -2657,7 +2654,7 @@
       <c r="F32" s="1">
         <v>0</v>
       </c>
-      <c r="G32" s="6" t="b">
+      <c r="G32" s="5" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="3">

--- a/Excel/MaskData.xlsx
+++ b/Excel/MaskData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="91">
   <si>
     <t>int</t>
   </si>
@@ -101,6 +101,9 @@
     <t>戴面具的资源对应的资源表的id</t>
   </si>
   <si>
+    <t>是否只是装饰物</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
   </si>
   <si>
     <t>resIdWithMask</t>
+  </si>
+  <si>
+    <t>isDecorator</t>
   </si>
   <si>
     <t>E_MaskType</t>
@@ -1465,7 +1471,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S32"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
@@ -1485,10 +1491,11 @@
     <col min="17" max="17" width="13.5555555555556" style="1" customWidth="1"/>
     <col min="18" max="18" width="13.1111111111111" style="1" customWidth="1"/>
     <col min="19" max="19" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.23148148148148" style="1"/>
+    <col min="20" max="20" width="12.4444444444444" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.23148148148148" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:19">
+    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1546,8 +1553,11 @@
       <c r="S1" s="1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="85" customHeight="1" spans="1:19">
+      <c r="T1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="85" customHeight="1" spans="1:20">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1605,69 +1615,75 @@
       <c r="S2" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:19">
+      <c r="T2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:20">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:19">
+        <v>43</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:20">
       <c r="A4" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1">
         <v>0</v>
@@ -1712,108 +1728,108 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:19">
+    <row r="5" s="1" customFormat="1" spans="1:20">
       <c r="A5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:19">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:20">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:19">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:20">
       <c r="C7" s="3"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:19">
+    <row r="8" s="1" customFormat="1" spans="1:20">
       <c r="C8" s="3"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -1821,7 +1837,7 @@
       <c r="G8" s="4"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:19">
+    <row r="9" s="1" customFormat="1" spans="1:20">
       <c r="C9" s="3"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -1829,7 +1845,7 @@
       <c r="G9" s="4"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:19">
+    <row r="10" s="1" customFormat="1" spans="1:20">
       <c r="C10" s="3"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -1837,7 +1853,7 @@
       <c r="G10" s="4"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:19">
+    <row r="11" s="1" customFormat="1" spans="1:20">
       <c r="C11" s="3"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1845,7 +1861,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:19">
+    <row r="12" s="1" customFormat="1" spans="1:20">
       <c r="C12" s="3"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1853,27 +1869,27 @@
       <c r="G12" s="4"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:19">
+    <row r="13" s="1" customFormat="1" spans="1:20">
       <c r="C13" s="3"/>
       <c r="G13" s="4"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:19">
+    <row r="14" s="1" customFormat="1" spans="1:20">
       <c r="C14" s="3"/>
       <c r="G14" s="4"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:19">
+    <row r="15" s="1" customFormat="1" spans="1:20">
       <c r="C15" s="3"/>
       <c r="G15" s="4"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="19" s="1" customFormat="1" spans="1:19">
+    <row r="19" s="1" customFormat="1" spans="1:20">
       <c r="A19" s="1">
         <v>10001</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C19" s="3">
         <v>20001</v>
@@ -1882,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F19" s="1">
         <v>5</v>
@@ -1894,7 +1910,7 @@
         <v>10026</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J19" s="1" t="b">
         <v>1</v>
@@ -1926,13 +1942,16 @@
       <c r="S19" s="1">
         <v>10015</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:19">
+      <c r="T19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:20">
       <c r="A20" s="1">
         <v>20001</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C20" s="3">
         <v>20002</v>
@@ -1941,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1953,7 +1972,7 @@
         <v>10026</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J20" s="1" t="b">
         <v>1</v>
@@ -1985,13 +2004,16 @@
       <c r="S20" s="1">
         <v>10004</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:19">
+      <c r="T20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:20">
       <c r="A21" s="1">
         <v>10002</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C21" s="3">
         <v>20003</v>
@@ -2000,7 +2022,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F21" s="1">
         <v>7</v>
@@ -2012,7 +2034,7 @@
         <v>10026</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J21" s="1" t="b">
         <v>1</v>
@@ -2044,13 +2066,16 @@
       <c r="S21" s="1">
         <v>10021</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:19">
+      <c r="T21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:20">
       <c r="A22" s="1">
         <v>10003</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C22" s="3">
         <v>20004</v>
@@ -2059,7 +2084,7 @@
         <v>3</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F22" s="1">
         <v>7</v>
@@ -2071,7 +2096,7 @@
         <v>10026</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J22" s="1" t="b">
         <v>1</v>
@@ -2103,13 +2128,16 @@
       <c r="S22" s="1">
         <v>10010</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:19">
+      <c r="T22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:20">
       <c r="A23" s="1">
         <v>10004</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C23" s="3">
         <v>20005</v>
@@ -2118,7 +2146,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F23" s="1">
         <v>5</v>
@@ -2130,7 +2158,7 @@
         <v>10026</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J23" s="1" t="b">
         <v>1</v>
@@ -2162,13 +2190,16 @@
       <c r="S23" s="1">
         <v>10008</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:19">
+      <c r="T23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:20">
       <c r="A24" s="1">
         <v>10005</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C24" s="3">
         <v>20006</v>
@@ -2177,7 +2208,7 @@
         <v>5</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F24" s="1">
         <v>5</v>
@@ -2189,7 +2220,7 @@
         <v>10026</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J24" s="1" t="b">
         <v>1</v>
@@ -2221,13 +2252,16 @@
       <c r="S24" s="1">
         <v>10012</v>
       </c>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="28.8" spans="1:19">
+      <c r="T24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="28.8" spans="1:20">
       <c r="A25" s="2">
         <v>20002</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C25" s="3">
         <v>20007</v>
@@ -2236,7 +2270,7 @@
         <v>6</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
@@ -2248,7 +2282,7 @@
         <v>10026</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J25" s="2" t="b">
         <v>1</v>
@@ -2280,13 +2314,16 @@
       <c r="S25" s="2">
         <v>10006</v>
       </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:19">
+      <c r="T25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:20">
       <c r="A26" s="1">
         <v>20003</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C26" s="3">
         <v>20008</v>
@@ -2295,7 +2332,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2307,7 +2344,7 @@
         <v>10026</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J26" s="1" t="b">
         <v>1</v>
@@ -2339,13 +2376,16 @@
       <c r="S26" s="1">
         <v>10017</v>
       </c>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="28.8" spans="1:19">
+      <c r="T26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="28.8" spans="1:20">
       <c r="A27" s="2">
         <v>20004</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C27" s="3">
         <v>20009</v>
@@ -2354,7 +2394,7 @@
         <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2366,7 +2406,7 @@
         <v>10026</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J27" s="2" t="b">
         <v>0</v>
@@ -2398,13 +2438,16 @@
       <c r="S27" s="2">
         <v>10019</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:19">
+      <c r="T27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:20">
       <c r="A28" s="1">
         <v>20005</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C28" s="3">
         <v>20010</v>
@@ -2413,7 +2456,7 @@
         <v>9</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F28" s="1">
         <v>0</v>
@@ -2425,7 +2468,7 @@
         <v>10026</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J28" s="1" t="b">
         <v>1</v>
@@ -2457,13 +2500,16 @@
       <c r="S28" s="1">
         <v>10002</v>
       </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:19">
+      <c r="T28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:20">
       <c r="A29" s="1">
         <v>20006</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C29" s="3">
         <v>20011</v>
@@ -2472,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2484,7 +2530,7 @@
         <v>10026</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J29" s="1" t="b">
         <v>1</v>
@@ -2516,13 +2562,16 @@
       <c r="S29" s="1">
         <v>10024</v>
       </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:19">
+      <c r="T29" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:20">
       <c r="A30" s="1">
         <v>20007</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C30" s="3">
         <v>20012</v>
@@ -2531,7 +2580,7 @@
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2543,7 +2592,7 @@
         <v>10026</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J30" s="1" t="b">
         <v>1</v>
@@ -2575,13 +2624,16 @@
       <c r="S30" s="1">
         <v>10023</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:19">
+      <c r="T30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:20">
       <c r="A31" s="1">
         <v>10006</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="3">
         <v>20011</v>
@@ -2590,7 +2642,7 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F31" s="1">
         <v>0</v>
@@ -2602,7 +2654,7 @@
         <v>10026</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J31" s="1" t="b">
         <v>1</v>
@@ -2634,13 +2686,16 @@
       <c r="S31" s="1">
         <v>10022</v>
       </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:19">
+      <c r="T31" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:20">
       <c r="A32" s="1">
         <v>10007</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C32" s="3">
         <v>20011</v>
@@ -2649,7 +2704,7 @@
         <v>13</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
@@ -2661,7 +2716,7 @@
         <v>10025</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J32" s="1" t="b">
         <v>1</v>
@@ -2692,6 +2747,9 @@
       </c>
       <c r="S32" s="1">
         <v>10013</v>
+      </c>
+      <c r="T32" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MaskData.xlsx
+++ b/Excel/MaskData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1472,30 +1472,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:T32"/>
-  <sheetFormatPr defaultColWidth="9.23148148148148" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9.23333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="2" width="15" style="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3055555555556" style="3" customWidth="1"/>
-    <col min="4" max="4" width="17.3055555555556" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.9907407407407" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.212962962963" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3083333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.3083333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.9916666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="28.2166666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="19.6666666666667" style="4" customWidth="1"/>
-    <col min="8" max="8" width="24.4444444444444" style="3" customWidth="1"/>
-    <col min="9" max="9" width="19.7777777777778" style="1" customWidth="1"/>
-    <col min="10" max="11" width="13.6111111111111" style="1" customWidth="1"/>
-    <col min="12" max="12" width="15.8518518518519" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.1111111111111" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.2222222222222" style="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5555555555556" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.4416666666667" style="3" customWidth="1"/>
+    <col min="9" max="9" width="19.775" style="1" customWidth="1"/>
+    <col min="10" max="11" width="13.6083333333333" style="1" customWidth="1"/>
+    <col min="12" max="12" width="15.85" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.1083333333333" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.225" style="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5583333333333" style="1" customWidth="1"/>
     <col min="16" max="16" width="12" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5555555555556" style="1" customWidth="1"/>
-    <col min="18" max="18" width="13.1111111111111" style="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5583333333333" style="1" customWidth="1"/>
+    <col min="18" max="18" width="13.1083333333333" style="1" customWidth="1"/>
     <col min="19" max="19" width="14.3333333333333" style="1" customWidth="1"/>
-    <col min="20" max="20" width="12.4444444444444" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.23148148148148" style="1"/>
+    <col min="20" max="20" width="12.4416666666667" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.23333333333333" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="28.8" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="27" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="28.8" spans="1:20">
+    <row r="3" s="1" customFormat="1" spans="1:20">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="28.8" spans="1:20">
+    <row r="6" s="1" customFormat="1" ht="27" spans="1:20">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="28.8" spans="1:20">
+    <row r="23" s="1" customFormat="1" ht="27" spans="1:20">
       <c r="A23" s="1">
         <v>10004</v>
       </c>
@@ -2256,7 +2256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="28.8" spans="1:20">
+    <row r="25" s="2" customFormat="1" ht="27" spans="1:20">
       <c r="A25" s="2">
         <v>20002</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" ht="28.8" spans="1:20">
+    <row r="27" s="2" customFormat="1" ht="27" spans="1:20">
       <c r="A27" s="2">
         <v>20004</v>
       </c>
